--- a/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2156,7 +2156,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-sortie-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-sortie-cisis|20260916095455</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>

--- a/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -634,7 +634,7 @@
     <t>estimatedDischargeDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.2.0}
 </t>
   </si>
   <si>
@@ -744,7 +744,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.2.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -830,7 +830,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1129,7 +1129,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.2.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1328,7 +1328,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.1.0|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1730,7 +1730,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0)
 </t>
   </si>
   <si>
@@ -2010,7 +2010,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -2245,7 +2245,7 @@
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -2275,7 +2275,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -8360,7 +8360,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
